--- a/insights/20251230-20241230-insights/Comparison_Salary_payroll.xlsx
+++ b/insights/20251230-20241230-insights/Comparison_Salary_payroll.xlsx
@@ -510,7 +510,7 @@
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -532,7 +532,7 @@
         <v>22</v>
       </c>
       <c r="C2" s="2">
-        <v>15136.990000</v>
+        <v>582.180000</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -543,7 +543,7 @@
         <v>23</v>
       </c>
       <c r="C3" s="2">
-        <v>4558.900000</v>
+        <v>175.340000</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -554,7 +554,7 @@
         <v>24</v>
       </c>
       <c r="C4" s="2">
-        <v>21369.860000</v>
+        <v>821.920000</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -565,7 +565,7 @@
         <v>25</v>
       </c>
       <c r="C5" s="2">
-        <v>24447.130000</v>
+        <v>940.280000</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -576,7 +576,7 @@
         <v>26</v>
       </c>
       <c r="C6" s="2">
-        <v>5502.740000</v>
+        <v>211.640000</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -587,7 +587,7 @@
         <v>27</v>
       </c>
       <c r="C7" s="2">
-        <v>4630.140000</v>
+        <v>178.080000</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -598,7 +598,7 @@
         <v>28</v>
       </c>
       <c r="C8" s="2">
-        <v>4772.600000</v>
+        <v>183.560000</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -609,7 +609,7 @@
         <v>29</v>
       </c>
       <c r="C9" s="2">
-        <v>16223.290000</v>
+        <v>623.970000</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -620,7 +620,7 @@
         <v>30</v>
       </c>
       <c r="C10" s="2">
-        <v>5858.900000</v>
+        <v>225.340000</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -631,7 +631,7 @@
         <v>31</v>
       </c>
       <c r="C11" s="2">
-        <v>4505.480000</v>
+        <v>173.290000</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -642,7 +642,7 @@
         <v>32</v>
       </c>
       <c r="C12" s="2">
-        <v>8084.930000</v>
+        <v>310.960000</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -653,7 +653,7 @@
         <v>33</v>
       </c>
       <c r="C13" s="2">
-        <v>24126.560000</v>
+        <v>927.940000</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -664,7 +664,7 @@
         <v>34</v>
       </c>
       <c r="C14" s="2">
-        <v>6500.000000</v>
+        <v>250.000000</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -675,7 +675,7 @@
         <v>35</v>
       </c>
       <c r="C15" s="2">
-        <v>5627.400000</v>
+        <v>216.440000</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -686,7 +686,7 @@
         <v>36</v>
       </c>
       <c r="C16" s="2">
-        <v>4630.140000</v>
+        <v>178.080000</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -697,7 +697,7 @@
         <v>37</v>
       </c>
       <c r="C17" s="2">
-        <v>9010.960000</v>
+        <v>346.570000</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -708,7 +708,7 @@
         <v>38</v>
       </c>
       <c r="C18" s="2">
-        <v>13142.460000</v>
+        <v>505.480000</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -719,7 +719,7 @@
         <v>39</v>
       </c>
       <c r="C19" s="2">
-        <v>4558.900000</v>
+        <v>175.340000</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -730,7 +730,7 @@
         <v>40</v>
       </c>
       <c r="C20" s="2">
-        <v>13427.400000</v>
+        <v>516.430000</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -741,7 +741,7 @@
         <v>41</v>
       </c>
       <c r="C21" s="2">
-        <v>5484.930000</v>
+        <v>210.960000</v>
       </c>
     </row>
   </sheetData>
